--- a/data/trans_orig/Q4505_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q4505_R-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia con la que utilizaron la sombra para evitar el sol el pasado verano al aire libre en 2007</t>
+          <t>Población según la frecuencia con la que utilizaron la sombra para evitar el sol el pasado verano al aire libre en 2007 (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>297994</t>
+          <t>297656</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>357390</t>
+          <t>355662</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>34,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>398799</t>
+          <t>402211</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>468959</t>
+          <t>469399</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>35,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>715019</t>
+          <t>719127</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>804300</t>
+          <t>807926</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>34,47%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>190891</t>
+          <t>193182</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>241555</t>
+          <t>244202</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>258346</t>
+          <t>261090</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>316547</t>
+          <t>320840</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>467158</t>
+          <t>468072</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>546870</t>
+          <t>550066</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,47%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>273042</t>
+          <t>272356</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>329281</t>
+          <t>330491</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>372254</t>
+          <t>365661</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>440677</t>
+          <t>434542</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>658141</t>
+          <t>661494</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>745528</t>
+          <t>747397</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>31,88%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>43003</t>
+          <t>42496</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>73487</t>
+          <t>73760</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>35709</t>
+          <t>35338</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>62162</t>
+          <t>62658</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>84201</t>
+          <t>86218</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>122370</t>
+          <t>126425</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,39%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>111943</t>
+          <t>110469</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>154876</t>
+          <t>156122</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>120148</t>
+          <t>119451</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>162473</t>
+          <t>162647</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>244479</t>
+          <t>243065</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>308557</t>
+          <t>305152</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,02%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>241799</t>
+          <t>241090</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>305791</t>
+          <t>301888</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>258752</t>
+          <t>259279</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>323551</t>
+          <t>323135</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>519920</t>
+          <t>518485</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>607155</t>
+          <t>603477</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,43%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>419952</t>
+          <t>419348</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>495744</t>
+          <t>487879</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>28,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>361052</t>
+          <t>360666</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>428848</t>
+          <t>425000</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>794491</t>
+          <t>798167</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>897062</t>
+          <t>899191</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>27,46%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>710581</t>
+          <t>715432</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>796706</t>
+          <t>794601</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>42,3%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>47,1%</t>
+          <t>46,98%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>668959</t>
+          <t>673416</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>749890</t>
+          <t>751332</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>42,25%</t>
+          <t>42,53%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>47,45%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1408783</t>
+          <t>1409554</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1522511</t>
+          <t>1521773</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>43,02%</t>
+          <t>43,04%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>46,49%</t>
+          <t>46,47%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>68474</t>
+          <t>70889</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>105154</t>
+          <t>109168</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>85159</t>
+          <t>84473</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>123295</t>
+          <t>125541</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>164164</t>
+          <t>164639</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>219088</t>
+          <t>216813</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,62%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>101478</t>
+          <t>101944</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>145916</t>
+          <t>143668</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>69982</t>
+          <t>70795</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>107610</t>
+          <t>107080</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>182709</t>
+          <t>179283</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>243219</t>
+          <t>239917</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,33%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>107612</t>
+          <t>107037</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>150470</t>
+          <t>148818</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>75911</t>
+          <t>75636</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>112092</t>
+          <t>111635</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>196794</t>
+          <t>192452</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>252208</t>
+          <t>247506</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,11%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>127922</t>
+          <t>127303</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>170965</t>
+          <t>171806</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>105578</t>
+          <t>105870</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>142682</t>
+          <t>144252</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>244527</t>
+          <t>243862</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>303445</t>
+          <t>302446</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,46%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>210045</t>
+          <t>209202</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>258384</t>
+          <t>255970</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>37,94%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>46,86%</t>
+          <t>46,42%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>173201</t>
+          <t>175571</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>216699</t>
+          <t>216209</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>36,44%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>45,6%</t>
+          <t>45,49%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>396840</t>
+          <t>396854</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>460422</t>
+          <t>462997</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>45,1%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14326</t>
+          <t>14708</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>35658</t>
+          <t>36162</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>24398</t>
+          <t>24137</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>47246</t>
+          <t>47533</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>43713</t>
+          <t>42382</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>74320</t>
+          <t>75198</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,32%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>11847</t>
+          <t>11975</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>30397</t>
+          <t>30143</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>18996</t>
+          <t>19183</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>40655</t>
+          <t>39819</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>36519</t>
+          <t>35722</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>64552</t>
+          <t>64185</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,25%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>676487</t>
+          <t>678719</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>776517</t>
+          <t>774598</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>765687</t>
+          <t>768582</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>867273</t>
+          <t>869708</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1476037</t>
+          <t>1476158</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1613255</t>
+          <t>1610915</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,24%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>772207</t>
+          <t>773493</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>875015</t>
+          <t>874795</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>760009</t>
+          <t>756407</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>860669</t>
+          <t>852152</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1552840</t>
+          <t>1561301</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1693811</t>
+          <t>1700355</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,59%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1234094</t>
+          <t>1231889</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1345973</t>
+          <t>1347753</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>37,63%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>41,12%</t>
+          <t>41,17%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1248466</t>
+          <t>1254114</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1363501</t>
+          <t>1368033</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>37,19%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>40,57%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2516420</t>
+          <t>2521219</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2674765</t>
+          <t>2677758</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>37,94%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>40,29%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>141363</t>
+          <t>142437</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>194459</t>
+          <t>194216</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>160219</t>
+          <t>158608</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>212550</t>
+          <t>214240</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>315701</t>
+          <t>314326</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>387548</t>
+          <t>392027</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,9%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>243172</t>
+          <t>243664</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>310391</t>
+          <t>306065</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>230443</t>
+          <t>229067</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>292128</t>
+          <t>290702</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>485180</t>
+          <t>485470</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>576290</t>
+          <t>573625</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,63%</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia con la que utilizaron la sombra para evitar el sol el pasado verano al aire libre en 2012</t>
+          <t>Población según la frecuencia con la que utilizaron la sombra para evitar el sol el pasado verano al aire libre en 2012 (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>397249</t>
+          <t>402630</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>461457</t>
+          <t>464215</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>40,8%</t>
+          <t>41,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>47,39%</t>
+          <t>47,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>655794</t>
+          <t>655787</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>730651</t>
+          <t>732186</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,83%</t>
+          <t>54,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1077673</t>
+          <t>1079975</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1177842</t>
+          <t>1174438</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>46,73%</t>
+          <t>46,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,07%</t>
+          <t>50,92%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>225024</t>
+          <t>225861</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>286854</t>
+          <t>281554</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>285219</t>
+          <t>287398</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>350604</t>
+          <t>351563</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>525658</t>
+          <t>533166</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>611438</t>
+          <t>614885</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,66%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>102608</t>
+          <t>103763</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>144674</t>
+          <t>146505</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>103282</t>
+          <t>103106</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>145651</t>
+          <t>146823</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>216919</t>
+          <t>217120</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>278082</t>
+          <t>279008</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4007,7 +4007,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,1%</t>
         </is>
       </c>
     </row>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11248</t>
+          <t>11247</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28841</t>
+          <t>28925</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4050,7 +4050,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6228</t>
+          <t>6714</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21520</t>
+          <t>21654</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>21107</t>
+          <t>20128</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>45656</t>
+          <t>43009</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -4143,12 +4143,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>124619</t>
+          <t>123458</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>172827</t>
+          <t>172102</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4158,12 +4158,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>160162</t>
+          <t>158723</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>213159</t>
+          <t>212693</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>295702</t>
+          <t>295638</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>367673</t>
+          <t>366026</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4233,7 +4233,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>15,87%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>571393</t>
+          <t>568521</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>652819</t>
+          <t>652591</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>33,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>531629</t>
+          <t>531749</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>610691</t>
+          <t>611307</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>34,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1124434</t>
+          <t>1124052</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1252654</t>
+          <t>1250075</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>33,73%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>635697</t>
+          <t>638755</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>724949</t>
+          <t>721410</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>539707</t>
+          <t>538282</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>621141</t>
+          <t>618383</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>35,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1202627</t>
+          <t>1196430</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1318977</t>
+          <t>1317313</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>35,54%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>382391</t>
+          <t>384616</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>456411</t>
+          <t>457588</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>357628</t>
+          <t>355856</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>432133</t>
+          <t>428403</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>756873</t>
+          <t>754770</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>860232</t>
+          <t>857557</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>23,14%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>43469</t>
+          <t>43410</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>73939</t>
+          <t>73039</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>48928</t>
+          <t>48670</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>81148</t>
+          <t>82101</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>99335</t>
+          <t>101083</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>146099</t>
+          <t>143702</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>166604</t>
+          <t>167571</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>221921</t>
+          <t>222382</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>122067</t>
+          <t>121548</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>171789</t>
+          <t>170670</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>303430</t>
+          <t>302856</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>374958</t>
+          <t>378942</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,22%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>115233</t>
+          <t>118106</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>158964</t>
+          <t>160520</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>140987</t>
+          <t>140242</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>183507</t>
+          <t>184823</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>40,34%</t>
+          <t>40,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>268552</t>
+          <t>268050</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>328584</t>
+          <t>328390</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>35,08%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>168117</t>
+          <t>166639</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>211727</t>
+          <t>213565</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>34,63%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>44,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>143553</t>
+          <t>142483</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>186579</t>
+          <t>185917</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>31,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,02%</t>
+          <t>40,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>325813</t>
+          <t>328116</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>390790</t>
+          <t>391930</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>41,75%</t>
+          <t>41,87%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>81863</t>
+          <t>80608</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>120083</t>
+          <t>118505</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>70871</t>
+          <t>70016</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>108648</t>
+          <t>105173</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>159839</t>
+          <t>161226</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>209568</t>
+          <t>213784</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,84%</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6106</t>
+          <t>6304</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21766</t>
+          <t>21912</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9124</t>
+          <t>9268</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>26768</t>
+          <t>27091</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>18556</t>
+          <t>18656</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>41020</t>
+          <t>41283</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,41%</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5507,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>30322</t>
+          <t>31069</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>59222</t>
+          <t>59060</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>16583</t>
+          <t>16797</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>37892</t>
+          <t>36805</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>51807</t>
+          <t>51781</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>86530</t>
+          <t>85695</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,16%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1122958</t>
+          <t>1128493</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1239290</t>
+          <t>1239660</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>33,06%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>36,32%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1370009</t>
+          <t>1361493</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1491622</t>
+          <t>1484294</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>38,75%</t>
+          <t>38,51%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>42,19%</t>
+          <t>41,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2524591</t>
+          <t>2525785</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2690789</t>
+          <t>2694282</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>38,77%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1067988</t>
+          <t>1066376</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1180319</t>
+          <t>1182669</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1007967</t>
+          <t>1001291</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1114610</t>
+          <t>1119231</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2106193</t>
+          <t>2099521</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2255457</t>
+          <t>2263502</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>32,57%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>592973</t>
+          <t>593564</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>689165</t>
+          <t>686128</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>556459</t>
+          <t>554598</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>649037</t>
+          <t>644255</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1175127</t>
+          <t>1173579</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1310540</t>
+          <t>1302066</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,74%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>70399</t>
+          <t>70620</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>109647</t>
+          <t>107102</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>73457</t>
+          <t>74042</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>113237</t>
+          <t>112695</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>151858</t>
+          <t>150936</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>207831</t>
+          <t>206309</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>345208</t>
+          <t>345452</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>425525</t>
+          <t>423562</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>319553</t>
+          <t>319526</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>391874</t>
+          <t>393824</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>675347</t>
+          <t>680918</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>785296</t>
+          <t>792072</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,4%</t>
         </is>
       </c>
     </row>
@@ -6455,7 +6455,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia con la que utilizaron la sombra para evitar el sol el pasado verano al aire libre en 2016</t>
+          <t>Población según la frecuencia con la que utilizaron la sombra para evitar el sol el pasado verano al aire libre en 2016 (tasa de respuesta: 99,67%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6650,12 +6650,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>235773</t>
+          <t>235720</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>286425</t>
+          <t>289231</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6665,12 +6665,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>38,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6685,12 +6685,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>331082</t>
+          <t>329378</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>394492</t>
+          <t>392415</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>33,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>39,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>582374</t>
+          <t>582016</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>663710</t>
+          <t>665000</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,04%</t>
+          <t>38,12%</t>
         </is>
       </c>
     </row>
@@ -6763,12 +6763,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>240101</t>
+          <t>239141</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>290964</t>
+          <t>290973</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6778,7 +6778,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6798,12 +6798,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>313123</t>
+          <t>314128</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>376689</t>
+          <t>376132</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>567462</t>
+          <t>568592</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>647713</t>
+          <t>647327</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>37,1%</t>
         </is>
       </c>
     </row>
@@ -6876,12 +6876,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>84761</t>
+          <t>82773</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>121297</t>
+          <t>117848</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6891,12 +6891,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>112610</t>
+          <t>112412</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>157553</t>
+          <t>155936</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>207599</t>
+          <t>208259</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>265067</t>
+          <t>264047</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,13%</t>
         </is>
       </c>
     </row>
@@ -6989,12 +6989,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12591</t>
+          <t>12517</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30157</t>
+          <t>29923</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7004,12 +7004,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7311</t>
+          <t>7427</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22387</t>
+          <t>21772</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7039,12 +7039,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>23496</t>
+          <t>22398</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>44434</t>
+          <t>44670</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7074,12 +7074,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,56%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>88444</t>
+          <t>87211</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>125204</t>
+          <t>123934</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>119469</t>
+          <t>118994</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>167799</t>
+          <t>165000</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>217474</t>
+          <t>219140</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>276691</t>
+          <t>279714</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>16,03%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>622793</t>
+          <t>621278</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>706814</t>
+          <t>707666</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>34,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>603462</t>
+          <t>609338</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>688417</t>
+          <t>688746</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>30,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>34,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1255911</t>
+          <t>1254792</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1375314</t>
+          <t>1375551</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7417,7 +7417,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>695123</t>
+          <t>696780</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>784377</t>
+          <t>785786</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>38,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>697442</t>
+          <t>697177</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>783311</t>
+          <t>787187</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7495,12 +7495,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>35,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>39,53%</t>
+          <t>39,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1422566</t>
+          <t>1422605</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1546292</t>
+          <t>1546642</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7535,7 +7535,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>38,21%</t>
         </is>
       </c>
     </row>
@@ -7558,12 +7558,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>399542</t>
+          <t>399596</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>477055</t>
+          <t>474786</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7578,7 +7578,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>377358</t>
+          <t>376950</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>449199</t>
+          <t>452744</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>797828</t>
+          <t>798188</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>903913</t>
+          <t>900504</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,25%</t>
         </is>
       </c>
     </row>
@@ -7671,12 +7671,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>45823</t>
+          <t>46325</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>76151</t>
+          <t>75990</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7686,12 +7686,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7706,12 +7706,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>35222</t>
+          <t>34416</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>63631</t>
+          <t>63467</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7721,12 +7721,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>87105</t>
+          <t>87786</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>129180</t>
+          <t>130227</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -7784,12 +7784,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>140200</t>
+          <t>142562</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>191667</t>
+          <t>193036</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7799,12 +7799,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7819,12 +7819,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>108950</t>
+          <t>106884</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>156655</t>
+          <t>154567</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7834,12 +7834,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>263191</t>
+          <t>264335</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>333628</t>
+          <t>332748</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,22%</t>
         </is>
       </c>
     </row>
@@ -8014,12 +8014,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>172547</t>
+          <t>170083</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>220083</t>
+          <t>219704</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8029,12 +8029,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>40,39%</t>
+          <t>40,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>176419</t>
+          <t>174843</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>221934</t>
+          <t>223264</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>40,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>359542</t>
+          <t>364411</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>426705</t>
+          <t>429888</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>33,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>39,29%</t>
         </is>
       </c>
     </row>
@@ -8127,12 +8127,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>186669</t>
+          <t>189278</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>234768</t>
+          <t>233703</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>34,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>42,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>180292</t>
+          <t>178102</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>225376</t>
+          <t>227004</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8177,12 +8177,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>32,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,04%</t>
+          <t>41,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>381058</t>
+          <t>379894</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>441862</t>
+          <t>444109</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,39%</t>
+          <t>40,59%</t>
         </is>
       </c>
     </row>
@@ -8240,12 +8240,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>83070</t>
+          <t>84517</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>121376</t>
+          <t>122358</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8255,12 +8255,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>87593</t>
+          <t>88615</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>124321</t>
+          <t>125582</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8290,12 +8290,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>183163</t>
+          <t>183134</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>235514</t>
+          <t>235478</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8330,7 +8330,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,52%</t>
         </is>
       </c>
     </row>
@@ -8353,12 +8353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6456</t>
+          <t>6950</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22480</t>
+          <t>22535</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8388,12 +8388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6930</t>
+          <t>6912</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>20836</t>
+          <t>21343</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8408,7 +8408,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>17526</t>
+          <t>16679</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>36567</t>
+          <t>37009</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8438,12 +8438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -8466,7 +8466,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>15586</t>
+          <t>15237</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -8481,7 +8481,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -8501,12 +8501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>19221</t>
+          <t>20473</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>43335</t>
+          <t>43073</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8516,12 +8516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>41970</t>
+          <t>39540</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>70842</t>
+          <t>71190</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,51%</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1061802</t>
+          <t>1063342</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1171519</t>
+          <t>1170653</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8711,12 +8711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>34,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1156443</t>
+          <t>1146519</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1270524</t>
+          <t>1266293</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>36,06%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2253101</t>
+          <t>2245630</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2413002</t>
+          <t>2408376</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>34,97%</t>
         </is>
       </c>
     </row>
@@ -8809,12 +8809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1160782</t>
+          <t>1163259</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1275661</t>
+          <t>1273855</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>37,87%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1225546</t>
+          <t>1227921</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1348068</t>
+          <t>1345891</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>38,26%</t>
+          <t>38,2%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2415813</t>
+          <t>2412768</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2579903</t>
+          <t>2583645</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>35,04%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>37,52%</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>591034</t>
+          <t>594217</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>686274</t>
+          <t>687483</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>607359</t>
+          <t>603719</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>697712</t>
+          <t>697938</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1221394</t>
+          <t>1220906</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1354644</t>
+          <t>1358209</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>19,72%</t>
         </is>
       </c>
     </row>
@@ -9035,12 +9035,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>75341</t>
+          <t>74615</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>115495</t>
+          <t>114596</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9050,12 +9050,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9070,12 +9070,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>56681</t>
+          <t>58471</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>90929</t>
+          <t>92948</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9085,12 +9085,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>142602</t>
+          <t>143502</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>191712</t>
+          <t>195270</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,84%</t>
         </is>
       </c>
     </row>
@@ -9148,12 +9148,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>264809</t>
+          <t>266172</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>330406</t>
+          <t>332282</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9183,12 +9183,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>267238</t>
+          <t>268096</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>333205</t>
+          <t>339651</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>557385</t>
+          <t>546211</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>649867</t>
+          <t>646423</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,39%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q4505_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q4505_R-Estudios-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>297656</t>
+          <t>299347</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>355662</t>
+          <t>354544</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>34,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>402211</t>
+          <t>402050</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>469399</t>
+          <t>469129</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>35,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>719127</t>
+          <t>712130</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>807926</t>
+          <t>805450</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>34,36%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>193182</t>
+          <t>193034</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>244202</t>
+          <t>243691</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>261090</t>
+          <t>261716</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>320840</t>
+          <t>322360</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>468072</t>
+          <t>470675</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>550066</t>
+          <t>546688</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,32%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>272356</t>
+          <t>273592</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>330491</t>
+          <t>329770</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>365661</t>
+          <t>369446</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>434542</t>
+          <t>435334</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>33,15%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>661494</t>
+          <t>658922</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>747397</t>
+          <t>747654</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>31,89%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>42496</t>
+          <t>42772</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>73760</t>
+          <t>71524</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>35338</t>
+          <t>35883</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>62658</t>
+          <t>61714</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>86218</t>
+          <t>84139</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>126425</t>
+          <t>124047</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,29%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>110469</t>
+          <t>109379</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>156122</t>
+          <t>152706</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>119451</t>
+          <t>120087</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>162647</t>
+          <t>163836</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>243065</t>
+          <t>243703</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>305152</t>
+          <t>303500</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>12,95%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>241090</t>
+          <t>243296</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>301888</t>
+          <t>303450</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>259279</t>
+          <t>259242</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>323135</t>
+          <t>320395</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>518485</t>
+          <t>519721</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>603477</t>
+          <t>606964</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,54%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>419348</t>
+          <t>420592</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>487879</t>
+          <t>492889</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>360666</t>
+          <t>363232</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>425000</t>
+          <t>428646</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>27,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>798167</t>
+          <t>802840</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>899191</t>
+          <t>902570</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,56%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>715432</t>
+          <t>713108</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>794601</t>
+          <t>794994</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>42,16%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>46,98%</t>
+          <t>47,0%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>673416</t>
+          <t>670751</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>751332</t>
+          <t>748700</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>42,53%</t>
+          <t>42,36%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>47,45%</t>
+          <t>47,29%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1409554</t>
+          <t>1411587</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1521773</t>
+          <t>1520841</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>43,04%</t>
+          <t>43,11%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>46,47%</t>
+          <t>46,44%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>70889</t>
+          <t>70029</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>109168</t>
+          <t>109240</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>84473</t>
+          <t>83843</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>125541</t>
+          <t>123915</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>164639</t>
+          <t>162546</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>216813</t>
+          <t>216210</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,6%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>101944</t>
+          <t>101421</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>143668</t>
+          <t>147244</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>70795</t>
+          <t>70259</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>107080</t>
+          <t>107852</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>179283</t>
+          <t>179595</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>239917</t>
+          <t>238090</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,27%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>107037</t>
+          <t>108558</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>148818</t>
+          <t>148300</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>75636</t>
+          <t>75762</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>111635</t>
+          <t>113062</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>192452</t>
+          <t>194863</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>247506</t>
+          <t>250343</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,38%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>127303</t>
+          <t>126180</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>171806</t>
+          <t>168900</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>105870</t>
+          <t>104417</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>144252</t>
+          <t>144126</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>243862</t>
+          <t>244277</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>302446</t>
+          <t>302708</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>29,48%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>209202</t>
+          <t>210875</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>255970</t>
+          <t>257682</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>37,94%</t>
+          <t>38,24%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>46,42%</t>
+          <t>46,73%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>175571</t>
+          <t>173126</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>216209</t>
+          <t>216636</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>45,49%</t>
+          <t>45,58%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>396854</t>
+          <t>390266</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>462997</t>
+          <t>458539</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>38,01%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>45,1%</t>
+          <t>44,66%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14708</t>
+          <t>14634</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>36162</t>
+          <t>35283</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>24137</t>
+          <t>24111</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>47533</t>
+          <t>47114</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>42382</t>
+          <t>43668</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>75198</t>
+          <t>73877</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,2%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>11975</t>
+          <t>12391</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>30143</t>
+          <t>30269</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>19183</t>
+          <t>19143</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>39819</t>
+          <t>40208</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>35722</t>
+          <t>36417</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>64185</t>
+          <t>63887</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,22%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>678719</t>
+          <t>674257</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>774598</t>
+          <t>774223</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>768582</t>
+          <t>767333</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>869708</t>
+          <t>865963</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1476158</t>
+          <t>1478653</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1610915</t>
+          <t>1616955</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,33%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>773493</t>
+          <t>765846</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>874795</t>
+          <t>868116</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>756407</t>
+          <t>754215</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>852152</t>
+          <t>857804</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1561301</t>
+          <t>1551499</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1700355</t>
+          <t>1695007</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,51%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1231889</t>
+          <t>1229065</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1347753</t>
+          <t>1347323</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>37,54%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>41,17%</t>
+          <t>41,16%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1254114</t>
+          <t>1253063</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1368033</t>
+          <t>1364092</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>37,19%</t>
+          <t>37,16%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>40,46%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2521219</t>
+          <t>2512973</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2677758</t>
+          <t>2668079</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>37,94%</t>
+          <t>37,81%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>40,29%</t>
+          <t>40,15%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>142437</t>
+          <t>141577</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>194216</t>
+          <t>193967</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>158608</t>
+          <t>159913</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>214240</t>
+          <t>213679</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>314326</t>
+          <t>317075</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>392027</t>
+          <t>386925</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,82%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>243664</t>
+          <t>243391</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>306065</t>
+          <t>306416</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>229067</t>
+          <t>227236</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>290702</t>
+          <t>286242</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>485470</t>
+          <t>488364</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>573625</t>
+          <t>575222</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,66%</t>
         </is>
       </c>
     </row>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>402630</t>
+          <t>397345</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>464215</t>
+          <t>462322</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>40,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>47,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>655787</t>
+          <t>658695</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>732186</t>
+          <t>733419</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>49,21%</t>
+          <t>49,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,94%</t>
+          <t>55,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1079975</t>
+          <t>1075731</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1174438</t>
+          <t>1174778</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>46,83%</t>
+          <t>46,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,92%</t>
+          <t>50,94%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>225861</t>
+          <t>226101</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>281554</t>
+          <t>281288</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>287398</t>
+          <t>286556</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>351563</t>
+          <t>349106</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>533166</t>
+          <t>532094</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>614885</t>
+          <t>620149</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,89%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>103763</t>
+          <t>102988</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>146505</t>
+          <t>148019</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>103106</t>
+          <t>102208</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>146823</t>
+          <t>146526</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>217120</t>
+          <t>218227</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>279008</t>
+          <t>284881</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,35%</t>
         </is>
       </c>
     </row>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11247</t>
+          <t>11033</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28925</t>
+          <t>29139</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6714</t>
+          <t>6249</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21654</t>
+          <t>22056</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>20128</t>
+          <t>20036</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>43009</t>
+          <t>43917</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -4143,12 +4143,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>123458</t>
+          <t>125031</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>172102</t>
+          <t>170888</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4158,12 +4158,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>158723</t>
+          <t>157548</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>212693</t>
+          <t>209781</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>295638</t>
+          <t>294393</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>366026</t>
+          <t>368852</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,99%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>568521</t>
+          <t>569687</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>652591</t>
+          <t>657617</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>531749</t>
+          <t>531195</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>611307</t>
+          <t>611427</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1124052</t>
+          <t>1123292</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1250075</t>
+          <t>1241129</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>33,48%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>638755</t>
+          <t>632117</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>721410</t>
+          <t>720901</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>36,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>538282</t>
+          <t>542215</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>618383</t>
+          <t>617267</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>35,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1196430</t>
+          <t>1192760</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1317313</t>
+          <t>1312259</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>32,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>35,4%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>384616</t>
+          <t>383618</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>457588</t>
+          <t>452311</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>355856</t>
+          <t>349999</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>428403</t>
+          <t>424461</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>754770</t>
+          <t>759292</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>857557</t>
+          <t>865982</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,36%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>43410</t>
+          <t>43414</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>73039</t>
+          <t>74758</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>48670</t>
+          <t>50199</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>82101</t>
+          <t>82735</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>101083</t>
+          <t>100995</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>143702</t>
+          <t>144731</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>167571</t>
+          <t>167181</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>222382</t>
+          <t>223496</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>121548</t>
+          <t>119499</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>170670</t>
+          <t>169055</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>302856</t>
+          <t>301388</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>378942</t>
+          <t>373264</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,07%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>118106</t>
+          <t>117602</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>160520</t>
+          <t>161774</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>33,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>140242</t>
+          <t>140915</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>184823</t>
+          <t>181803</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>40,63%</t>
+          <t>39,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>268050</t>
+          <t>271567</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>328390</t>
+          <t>331252</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>35,39%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>166639</t>
+          <t>169150</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>213565</t>
+          <t>214180</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>44,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>142483</t>
+          <t>144639</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>185917</t>
+          <t>187679</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>31,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>40,87%</t>
+          <t>41,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>328116</t>
+          <t>322665</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>391930</t>
+          <t>388224</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>41,87%</t>
+          <t>41,48%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>80608</t>
+          <t>80461</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>118505</t>
+          <t>117823</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>70016</t>
+          <t>69973</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>105173</t>
+          <t>104789</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>161226</t>
+          <t>159221</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>213784</t>
+          <t>212791</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,73%</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6304</t>
+          <t>6001</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21912</t>
+          <t>20903</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9268</t>
+          <t>9765</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>27091</t>
+          <t>26309</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>18656</t>
+          <t>17613</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>41283</t>
+          <t>40972</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,38%</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5507,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>31069</t>
+          <t>30260</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>59060</t>
+          <t>57540</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>16797</t>
+          <t>16698</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>36805</t>
+          <t>36715</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>51781</t>
+          <t>51464</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>85695</t>
+          <t>88051</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,41%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1128493</t>
+          <t>1126804</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1239660</t>
+          <t>1237989</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>33,01%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>36,27%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1361493</t>
+          <t>1368354</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1484294</t>
+          <t>1486170</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>38,51%</t>
+          <t>38,7%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>41,98%</t>
+          <t>42,03%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2525785</t>
+          <t>2523124</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2694282</t>
+          <t>2687843</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>36,35%</t>
+          <t>36,31%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>38,77%</t>
+          <t>38,68%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1066376</t>
+          <t>1069411</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1182669</t>
+          <t>1179545</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1001291</t>
+          <t>1008109</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1119231</t>
+          <t>1120422</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2099521</t>
+          <t>2097352</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2263502</t>
+          <t>2254911</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>32,45%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>593564</t>
+          <t>589698</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>686128</t>
+          <t>688212</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>554598</t>
+          <t>556638</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>644255</t>
+          <t>646589</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1173579</t>
+          <t>1169756</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1302066</t>
+          <t>1306398</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,8%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>70620</t>
+          <t>69626</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>107102</t>
+          <t>108305</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>74042</t>
+          <t>75023</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>112695</t>
+          <t>112801</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>150936</t>
+          <t>155150</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>206309</t>
+          <t>208970</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>345452</t>
+          <t>343162</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>423562</t>
+          <t>420633</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>319526</t>
+          <t>315151</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>393824</t>
+          <t>390301</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>680918</t>
+          <t>686034</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>792072</t>
+          <t>795888</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,45%</t>
         </is>
       </c>
     </row>
@@ -6650,12 +6650,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>235720</t>
+          <t>234908</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>289231</t>
+          <t>285887</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6665,12 +6665,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>38,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6685,12 +6685,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>329378</t>
+          <t>331042</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>392415</t>
+          <t>395678</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,55%</t>
+          <t>39,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>582016</t>
+          <t>582755</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>665000</t>
+          <t>663446</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>33,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,12%</t>
+          <t>38,03%</t>
         </is>
       </c>
     </row>
@@ -6763,12 +6763,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>239141</t>
+          <t>238279</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>290973</t>
+          <t>291184</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6778,12 +6778,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>31,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,67%</t>
+          <t>38,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6798,12 +6798,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>314128</t>
+          <t>309230</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>376132</t>
+          <t>374929</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>568592</t>
+          <t>564485</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>647327</t>
+          <t>651795</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>37,1%</t>
+          <t>37,36%</t>
         </is>
       </c>
     </row>
@@ -6876,12 +6876,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>82773</t>
+          <t>83577</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>117848</t>
+          <t>121322</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6891,12 +6891,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>112412</t>
+          <t>111991</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>155936</t>
+          <t>155061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>208259</t>
+          <t>207724</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>264047</t>
+          <t>265378</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,21%</t>
         </is>
       </c>
     </row>
@@ -6989,12 +6989,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12517</t>
+          <t>13517</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29923</t>
+          <t>31352</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7004,12 +7004,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7427</t>
+          <t>6932</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21772</t>
+          <t>21102</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7039,12 +7039,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22398</t>
+          <t>23000</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>44670</t>
+          <t>46229</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7074,12 +7074,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>87211</t>
+          <t>87371</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>123934</t>
+          <t>124496</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>118994</t>
+          <t>119165</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>165000</t>
+          <t>168294</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>219140</t>
+          <t>216580</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>279714</t>
+          <t>277661</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>15,92%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>621278</t>
+          <t>621568</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>707666</t>
+          <t>708921</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>609338</t>
+          <t>611493</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>688746</t>
+          <t>692713</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>34,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1254792</t>
+          <t>1255131</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1375551</t>
+          <t>1379914</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>34,09%</t>
         </is>
       </c>
     </row>
@@ -7445,12 +7445,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>696780</t>
+          <t>697893</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>785786</t>
+          <t>780706</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>33,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>697177</t>
+          <t>699283</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>787187</t>
+          <t>781802</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7495,47 +7495,47 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
+          <t>35,29%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>39,45%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>1418</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>1481824</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>1423890</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>1545810</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>36,61%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
           <t>35,18%</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>39,72%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>1418</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>1481824</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>1422605</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>1546642</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>36,61%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>35,15%</t>
-        </is>
-      </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>38,19%</t>
         </is>
       </c>
     </row>
@@ -7558,12 +7558,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>399596</t>
+          <t>399292</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>474786</t>
+          <t>472486</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>376950</t>
+          <t>379921</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>452744</t>
+          <t>450126</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>798188</t>
+          <t>797015</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>900504</t>
+          <t>905274</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,37%</t>
         </is>
       </c>
     </row>
@@ -7671,12 +7671,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>46325</t>
+          <t>45979</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>75990</t>
+          <t>76745</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7686,12 +7686,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7706,12 +7706,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>34416</t>
+          <t>35282</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>63467</t>
+          <t>64137</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7721,47 +7721,47 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
+          <t>3,24%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>106955</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>88612</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>129347</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>2,64%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>2,19%</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
           <t>3,2%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>106955</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>87786</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>130227</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>2,64%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>2,17%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -7784,12 +7784,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>142562</t>
+          <t>144765</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>193036</t>
+          <t>193844</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7799,12 +7799,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7819,12 +7819,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>106884</t>
+          <t>107041</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>154567</t>
+          <t>155247</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7834,12 +7834,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>264335</t>
+          <t>265875</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>332748</t>
+          <t>335893</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,3%</t>
         </is>
       </c>
     </row>
@@ -8014,12 +8014,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>170083</t>
+          <t>170720</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>219704</t>
+          <t>219524</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8029,12 +8029,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>40,32%</t>
+          <t>40,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>174843</t>
+          <t>174763</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>223264</t>
+          <t>221183</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>31,82%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>40,66%</t>
+          <t>40,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>364411</t>
+          <t>362131</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>429888</t>
+          <t>428204</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>39,14%</t>
         </is>
       </c>
     </row>
@@ -8127,12 +8127,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>189278</t>
+          <t>186396</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>233703</t>
+          <t>234509</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>43,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>178102</t>
+          <t>182568</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>227004</t>
+          <t>226694</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8177,12 +8177,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,34%</t>
+          <t>41,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>379894</t>
+          <t>379604</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>444109</t>
+          <t>443893</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>34,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,59%</t>
+          <t>40,57%</t>
         </is>
       </c>
     </row>
@@ -8240,12 +8240,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>84517</t>
+          <t>84058</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>122358</t>
+          <t>121782</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8255,12 +8255,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>88615</t>
+          <t>89883</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>125582</t>
+          <t>126390</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8290,12 +8290,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>183134</t>
+          <t>179779</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>235478</t>
+          <t>232999</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,3%</t>
         </is>
       </c>
     </row>
@@ -8353,12 +8353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6950</t>
+          <t>7015</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22535</t>
+          <t>22125</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8388,12 +8388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6912</t>
+          <t>7128</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21343</t>
+          <t>21990</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8403,12 +8403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>16679</t>
+          <t>16932</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>37009</t>
+          <t>37919</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8438,12 +8438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,47%</t>
         </is>
       </c>
     </row>
@@ -8466,12 +8466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>15237</t>
+          <t>15363</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>37023</t>
+          <t>37082</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8481,12 +8481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8501,12 +8501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>20473</t>
+          <t>19759</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>43073</t>
+          <t>41814</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8516,12 +8516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>39540</t>
+          <t>40644</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>71190</t>
+          <t>70604</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,45%</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1063342</t>
+          <t>1068712</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1170653</t>
+          <t>1175226</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8711,12 +8711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>34,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1146519</t>
+          <t>1155990</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1266293</t>
+          <t>1270989</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2245630</t>
+          <t>2255817</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2408376</t>
+          <t>2415059</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>35,07%</t>
         </is>
       </c>
     </row>
@@ -8809,12 +8809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1163259</t>
+          <t>1153690</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1273855</t>
+          <t>1266955</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1227921</t>
+          <t>1230191</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1345891</t>
+          <t>1343518</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>38,14%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2412768</t>
+          <t>2424956</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2583645</t>
+          <t>2588283</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>37,59%</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>594217</t>
+          <t>595738</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>687483</t>
+          <t>686205</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>603719</t>
+          <t>607352</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>697938</t>
+          <t>702534</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1220906</t>
+          <t>1227656</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1358209</t>
+          <t>1360435</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,76%</t>
         </is>
       </c>
     </row>
@@ -9035,12 +9035,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>74615</t>
+          <t>75591</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>114596</t>
+          <t>111889</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9050,12 +9050,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9070,12 +9070,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>58471</t>
+          <t>56398</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>92948</t>
+          <t>91311</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9085,12 +9085,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>143502</t>
+          <t>140865</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>195270</t>
+          <t>193226</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -9148,12 +9148,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>266172</t>
+          <t>263981</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>332282</t>
+          <t>328658</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9183,12 +9183,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>268096</t>
+          <t>268412</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>339651</t>
+          <t>337152</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>546211</t>
+          <t>545924</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>646423</t>
+          <t>642860</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9238,7 +9238,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,34%</t>
         </is>
       </c>
     </row>
